--- a/exports/ca_taxalpha_report_demo.xlsx
+++ b/exports/ca_taxalpha_report_demo.xlsx
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated on 2026-09-25 21:36 | Applicable FY: All Financial Years</t>
+          <t>Generated on 2026-09-25 22:29 | Applicable FY: All Financial Years</t>
         </is>
       </c>
     </row>
